--- a/xlsx/system@系统.xlsx
+++ b/xlsx/system@系统.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\excelparser\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\excelparser\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B285ECF9-B1A4-47C2-B846-AD91993E03DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF448EF-6FF9-43F8-9FD8-88FACAA93BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>int</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -66,10 +66,6 @@
   </si>
   <si>
     <t>key1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>简单字典</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -118,6 +114,26 @@
   </si>
   <si>
     <t>json:[][]int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单数组</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>json结构体</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>key8</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>json:{sites=[][]{id=int,name=string},age=int}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"sites":[[{"id":1,"name":"test001"}]],"age":123}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -11626,14 +11642,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -11656,14 +11672,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -11671,7 +11687,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4" t="s">
@@ -11686,7 +11702,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4" t="s">
@@ -11701,7 +11717,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4" t="s">
@@ -11713,14 +11729,14 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
@@ -11746,7 +11762,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="6">
         <v>5</v>
@@ -11754,17 +11770,32 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/system@系统.xlsx
+++ b/xlsx/system@系统.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\excelparser\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF448EF-6FF9-43F8-9FD8-88FACAA93BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBA339B-D9BA-49FB-B24A-D88714749DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t>int</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -136,6 +136,61 @@
     <t>{"sites":[[{"id":1,"name":"test001"}]],"age":123}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
+  <si>
+    <t>key9</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>map[int]map[int]string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵌套map</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>map[int]string</t>
+  </si>
+  <si>
+    <t>val1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>外层key1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>外层val1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>hello</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>外层key2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>外层val2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>world</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuck</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>val2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>you</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -8543,7 +8598,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8557,10 +8612,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="268" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="268" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2777">
@@ -11642,14 +11694,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -11678,7 +11730,7 @@
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -11798,6 +11850,171 @@
         <v>27</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
